--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_10.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_10.xlsx
@@ -676,7 +676,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -850,7 +850,7 @@
     <t>Mancini</t>
   </si>
   <si>
-    <t>N'dicka</t>
+    <t>N'Dicka</t>
   </si>
   <si>
     <t>Celik</t>
